--- a/artfynd/A 49151-2024 artfynd.xlsx
+++ b/artfynd/A 49151-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119586862</v>
+        <v>119586861</v>
       </c>
       <c r="B2" t="n">
-        <v>74622</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6439</v>
+        <v>535</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>384401</v>
+        <v>384394</v>
       </c>
       <c r="R2" t="n">
-        <v>6295437</v>
+        <v>6295428</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,21 +756,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>bok</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,50 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119586864</v>
+        <v>119586842</v>
       </c>
       <c r="B3" t="n">
-        <v>43677</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79840</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101735</v>
+        <v>1027</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Pulverädellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Megalaria pulverea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Borrer) Hafellner &amp; E.Schreiner</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Berget/Spjutaberget, Hl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>384386</v>
+        <v>384449</v>
       </c>
       <c r="R3" t="n">
-        <v>6295471</v>
+        <v>6295383</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,22 +854,23 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,15 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119586863</v>
+        <v>119586865</v>
       </c>
       <c r="B4" t="n">
-        <v>74622</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97811</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6439</v>
+        <v>2604</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>384401</v>
+        <v>384352</v>
       </c>
       <c r="R4" t="n">
-        <v>6295439</v>
+        <v>6295548</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,6 +997,1322 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>119586839</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97785</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2606</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Klippfrullania</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Frullania tamarisci</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Berget/Spjutaberget, Hl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>384456</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6295400</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Enslöv</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>119586838</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96231</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Berget/Spjutaberget, Hl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>384452</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6295404</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Enslöv</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>119586860</v>
+      </c>
+      <c r="B7" t="n">
+        <v>83290</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Berget/Spjutaberget, Hl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>384394</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6295426</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Enslöv</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>119586862</v>
+      </c>
+      <c r="B8" t="n">
+        <v>83290</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Berget/Spjutaberget, Hl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>384401</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6295437</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Enslöv</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>119586863</v>
+      </c>
+      <c r="B9" t="n">
+        <v>83290</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Berget/Spjutaberget, Hl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>384401</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6295439</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Enslöv</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>106663525</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56830</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bräknesbacken, Hl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>384347</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6295483</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Enslöv</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-08-15</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Autoboxlokal</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>119586841</v>
+      </c>
+      <c r="B11" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Berget/Spjutaberget, Hl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>384463</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6295391</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Enslöv</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>119586864</v>
+      </c>
+      <c r="B12" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Berget/Spjutaberget, Hl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>384386</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6295471</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Enslöv</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>106664909</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56823</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bräknesbacken, Hl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>384347</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6295483</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Enslöv</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-08-15</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Autoboxlokal</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>106660533</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bräknesbacken, Hl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>384347</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6295483</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Enslöv</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-08-15</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Autoboxlokal</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>106662054</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bräknesbacken, Hl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>384347</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6295483</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Enslöv</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-08-15</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Autoboxlokal</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49151-2024 artfynd.xlsx
+++ b/artfynd/A 49151-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119586861</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119586842</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119586865</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,6 +1129,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119586839</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1221,6 +1246,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119586838</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1333,6 +1363,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119586860</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1445,6 +1480,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119586862</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1557,6 +1597,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119586863</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1690,6 +1735,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106663525</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1802,6 +1852,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119586841</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1914,6 +1969,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119586864</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2047,6 +2107,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106664909</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2180,6 +2245,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106660533</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2313,8 +2383,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106662054</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>